--- a/data/trans_dic/P16A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,92</t>
+          <t>4,62; 10,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 17,42</t>
+          <t>8,98; 17,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 14,95</t>
+          <t>7,68; 15,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,72</t>
+          <t>5,24; 12,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 11,18</t>
+          <t>4,48; 11,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,89</t>
+          <t>8,08; 16,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,23</t>
+          <t>5,9; 12,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,48</t>
+          <t>4,84; 9,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,94</t>
+          <t>5,27; 9,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 15,09</t>
+          <t>9,42; 14,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,67</t>
+          <t>7,6; 12,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,98</t>
+          <t>5,42; 10,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,88</t>
+          <t>4,32; 8,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 16,23</t>
+          <t>9,99; 16,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,73</t>
+          <t>5,12; 9,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,21</t>
+          <t>1,98; 6,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,91</t>
+          <t>4,27; 8,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,23</t>
+          <t>6,32; 11,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,44; 10,23</t>
+          <t>5,37; 10,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,45</t>
+          <t>4,79; 9,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,22</t>
+          <t>4,81; 7,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 12,6</t>
+          <t>8,76; 12,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,08</t>
+          <t>5,74; 9,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,87</t>
+          <t>3,83; 6,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,22</t>
+          <t>2,53; 7,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 14,8</t>
+          <t>8,1; 14,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,92</t>
+          <t>3,73; 9,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 10,1</t>
+          <t>4,51; 9,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,14</t>
+          <t>0,86; 3,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 14,7</t>
+          <t>7,34; 14,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,25</t>
+          <t>5,05; 11,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,96</t>
+          <t>6,88; 12,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,91</t>
+          <t>2,04; 4,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,61; 13,56</t>
+          <t>8,48; 13,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,14</t>
+          <t>5,09; 9,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,13</t>
+          <t>6,45; 10,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,54</t>
+          <t>3,71; 8,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,08</t>
+          <t>4,2; 9,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,04</t>
+          <t>6,42; 12,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 13,32</t>
+          <t>5,15; 13,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,01</t>
+          <t>3,35; 7,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 13,24</t>
+          <t>6,8; 13,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,87</t>
+          <t>4,69; 9,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,78</t>
+          <t>3,38; 8,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,51</t>
+          <t>3,88; 7,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,14</t>
+          <t>6,3; 10,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,97</t>
+          <t>6,12; 9,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,43</t>
+          <t>4,56; 9,53</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,11</t>
+          <t>4,17; 11,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 17,76</t>
+          <t>8,15; 17,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 10,33</t>
+          <t>3,59; 10,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,62</t>
+          <t>4,41; 10,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,52</t>
+          <t>3,92; 11,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 14,6</t>
+          <t>6,31; 14,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,82</t>
+          <t>5,04; 12,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 15,24</t>
+          <t>8,61; 15,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,99</t>
+          <t>5,06; 10,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,87; 14,45</t>
+          <t>8,18; 14,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,87</t>
+          <t>5,1; 10,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,36; 11,9</t>
+          <t>7,16; 11,87</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,56</t>
+          <t>3,88; 9,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,05; 20,13</t>
+          <t>11,19; 20,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,02</t>
+          <t>4,09; 10,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,8</t>
+          <t>5,7; 11,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 9,04</t>
+          <t>3,19; 8,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,18; 14,22</t>
+          <t>7,15; 14,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 12,89</t>
+          <t>6,42; 13,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,09</t>
+          <t>5,06; 10,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,14; 8,01</t>
+          <t>4,09; 7,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 15,67</t>
+          <t>9,92; 15,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,76</t>
+          <t>5,96; 10,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,96</t>
+          <t>5,88; 10,01</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,39</t>
+          <t>5,9; 10,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,25</t>
+          <t>6,12; 10,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,87</t>
+          <t>6,18; 10,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 14,15</t>
+          <t>7,78; 14,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,39</t>
+          <t>4,5; 8,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,16</t>
+          <t>4,31; 8,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,85</t>
+          <t>5,59; 9,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 10,35</t>
+          <t>3,49; 10,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,47</t>
+          <t>5,59; 8,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,91</t>
+          <t>6,01; 8,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 9,81</t>
+          <t>6,53; 9,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 10,98</t>
+          <t>5,67; 10,91</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,43</t>
+          <t>6,31; 10,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,04</t>
+          <t>3,51; 7,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,84</t>
+          <t>5,27; 8,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,77</t>
+          <t>1,6; 5,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,12</t>
+          <t>6,86; 11,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,15</t>
+          <t>4,65; 7,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,2</t>
+          <t>7,83; 12,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,66</t>
+          <t>4,68; 7,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,0</t>
+          <t>7,08; 10,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,99</t>
+          <t>4,61; 7,08</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,0</t>
+          <t>7,03; 9,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,08</t>
+          <t>2,85; 5,99</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,01; 7,81</t>
+          <t>6,07; 7,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,47; 10,67</t>
+          <t>8,38; 10,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,79; 8,73</t>
+          <t>6,76; 8,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,67</t>
+          <t>5,08; 7,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,35</t>
+          <t>5,6; 7,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,48; 9,31</t>
+          <t>7,42; 9,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,28</t>
+          <t>7,37; 9,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,12</t>
+          <t>5,86; 8,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,37</t>
+          <t>6,02; 7,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,16; 9,58</t>
+          <t>8,14; 9,59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,66</t>
+          <t>7,35; 8,73</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,73</t>
+          <t>5,96; 7,71</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el catarro en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11768; 29799</t>
+          <t>12605; 29953</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25813; 50540</t>
+          <t>26048; 50252</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21622; 43916</t>
+          <t>22554; 44517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15480; 39613</t>
+          <t>16324; 38851</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11197; 29175</t>
+          <t>11680; 29185</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21211; 44536</t>
+          <t>22638; 45339</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17113; 38206</t>
+          <t>17028; 35792</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14023; 27444</t>
+          <t>14024; 27650</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27410; 53041</t>
+          <t>28117; 52831</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53800; 86086</t>
+          <t>53758; 85206</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44592; 73802</t>
+          <t>44264; 72842</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33698; 59990</t>
+          <t>32568; 62335</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21611; 43795</t>
+          <t>21319; 44013</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50191; 82039</t>
+          <t>50497; 83581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25475; 48913</t>
+          <t>25714; 49316</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10502; 32125</t>
+          <t>10251; 31534</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21899; 44925</t>
+          <t>21543; 43157</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33030; 58679</t>
+          <t>33027; 57816</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28440; 53517</t>
+          <t>28071; 54670</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24860; 48465</t>
+          <t>24550; 47838</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49990; 81961</t>
+          <t>47928; 78616</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91169; 129563</t>
+          <t>90112; 132005</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59793; 93091</t>
+          <t>58888; 94486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38860; 70749</t>
+          <t>39422; 71993</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8109; 23030</t>
+          <t>8067; 22822</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24794; 47823</t>
+          <t>26162; 48445</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11408; 28404</t>
+          <t>11897; 28660</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14449; 31927</t>
+          <t>14252; 30829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3020; 13901</t>
+          <t>2872; 13331</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26738; 50115</t>
+          <t>25027; 48137</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16643; 37826</t>
+          <t>16981; 38744</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23937; 41750</t>
+          <t>24006; 43063</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13310; 32095</t>
+          <t>13364; 30412</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57213; 90059</t>
+          <t>56343; 88125</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32176; 59825</t>
+          <t>33358; 60001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42544; 67386</t>
+          <t>42877; 67005</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13533; 30627</t>
+          <t>13301; 30502</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14938; 33954</t>
+          <t>15693; 36469</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22522; 44550</t>
+          <t>23765; 44837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15680; 41630</t>
+          <t>16083; 42201</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12788; 29759</t>
+          <t>12441; 29161</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27821; 51381</t>
+          <t>26392; 51090</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17476; 38207</t>
+          <t>18175; 37597</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16277; 41762</t>
+          <t>16063; 41195</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30314; 54843</t>
+          <t>28352; 53085</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45523; 77273</t>
+          <t>48009; 79128</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46759; 75494</t>
+          <t>46371; 75519</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35056; 74316</t>
+          <t>35902; 75101</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8896; 22587</t>
+          <t>8471; 22713</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17132; 37758</t>
+          <t>17335; 37500</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7566; 21824</t>
+          <t>7584; 22543</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7993; 18985</t>
+          <t>7879; 18933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8534; 23928</t>
+          <t>8133; 23144</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13549; 32071</t>
+          <t>13853; 32435</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10850; 25837</t>
+          <t>11017; 27094</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18052; 31803</t>
+          <t>17975; 31924</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20760; 41051</t>
+          <t>20776; 41211</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34036; 62447</t>
+          <t>35362; 62668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22519; 42408</t>
+          <t>21902; 43191</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28505; 46119</t>
+          <t>27755; 45979</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10430; 25879</t>
+          <t>10516; 25801</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30280; 55152</t>
+          <t>30657; 54902</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11126; 28998</t>
+          <t>10765; 27931</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14228; 31819</t>
+          <t>15370; 31947</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9025; 25136</t>
+          <t>8859; 25009</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20049; 39692</t>
+          <t>19963; 41333</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16346; 35196</t>
+          <t>17523; 35955</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13015; 25928</t>
+          <t>13014; 27051</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22719; 43995</t>
+          <t>22478; 43435</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54466; 86662</t>
+          <t>54883; 86935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31667; 57682</t>
+          <t>31978; 57012</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>31589; 52478</t>
+          <t>30982; 52728</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>37194; 63906</t>
+          <t>36289; 63302</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43054; 74583</t>
+          <t>40576; 71521</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41568; 71348</t>
+          <t>40571; 69709</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49230; 88313</t>
+          <t>48568; 87601</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29342; 53572</t>
+          <t>28727; 53645</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31905; 56604</t>
+          <t>29914; 56485</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40016; 68083</t>
+          <t>38667; 67225</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>30331; 87883</t>
+          <t>29641; 88088</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>69683; 106125</t>
+          <t>70098; 106909</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78884; 120941</t>
+          <t>81580; 121843</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88614; 132174</t>
+          <t>88073; 129469</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>77824; 161854</t>
+          <t>83573; 160782</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>49227; 77471</t>
+          <t>46880; 77090</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27181; 54729</t>
+          <t>27275; 55090</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40880; 68788</t>
+          <t>41061; 69502</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>17128; 53551</t>
+          <t>14827; 54511</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>54735; 87110</t>
+          <t>53779; 86238</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38685; 66832</t>
+          <t>38186; 65410</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>64348; 100813</t>
+          <t>64725; 102535</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33654; 54787</t>
+          <t>33462; 53636</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>110117; 152616</t>
+          <t>108137; 153106</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>72894; 111682</t>
+          <t>73650; 113171</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>113098; 160419</t>
+          <t>112746; 159678</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>48904; 99972</t>
+          <t>46765; 98407</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>196981; 255794</t>
+          <t>198803; 256265</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>289602; 364737</t>
+          <t>286616; 357926</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>230616; 296394</t>
+          <t>229355; 294465</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>174870; 265333</t>
+          <t>175822; 267910</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>187296; 248215</t>
+          <t>189238; 247559</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>265277; 330185</t>
+          <t>262955; 336776</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>261087; 328950</t>
+          <t>261307; 330404</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>211773; 296798</t>
+          <t>214202; 295894</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>405507; 490355</t>
+          <t>400407; 487562</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>568021; 667252</t>
+          <t>566712; 667732</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>508103; 600878</t>
+          <t>510177; 605538</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>428685; 549704</t>
+          <t>424323; 548369</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A01-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P16A01-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,97</t>
+          <t>4,44; 10,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 17,32</t>
+          <t>9,26; 17,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 15,15</t>
+          <t>7,68; 14,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 12,47</t>
+          <t>4,88; 11,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 11,19</t>
+          <t>4,31; 11,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 16,17</t>
+          <t>7,94; 15,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,4</t>
+          <t>6,19; 12,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,55</t>
+          <t>4,72; 9,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,9</t>
+          <t>5,12; 9,65</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 14,93</t>
+          <t>9,52; 14,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 12,51</t>
+          <t>7,84; 12,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,37</t>
+          <t>5,31; 9,01</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,93</t>
+          <t>4,34; 9,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 16,53</t>
+          <t>10,08; 16,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,81</t>
+          <t>5,04; 9,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,09</t>
+          <t>1,99; 5,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,56</t>
+          <t>4,38; 8,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,06</t>
+          <t>6,29; 11,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 10,45</t>
+          <t>5,32; 10,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,33</t>
+          <t>4,7; 9,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,89</t>
+          <t>5,03; 8,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,76; 12,84</t>
+          <t>8,63; 12,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,21</t>
+          <t>5,89; 9,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 6,99</t>
+          <t>3,79; 6,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,16</t>
+          <t>2,43; 7,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 14,99</t>
+          <t>7,77; 14,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,0</t>
+          <t>3,91; 9,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 9,75</t>
+          <t>5,12; 11,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,97</t>
+          <t>0,84; 3,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,12</t>
+          <t>7,63; 14,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 11,52</t>
+          <t>4,76; 11,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,88; 12,33</t>
+          <t>7,37; 12,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,65</t>
+          <t>2,01; 4,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 13,27</t>
+          <t>8,54; 13,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,16</t>
+          <t>4,91; 9,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,07</t>
+          <t>6,97; 10,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,5</t>
+          <t>3,66; 8,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 9,75</t>
+          <t>4,02; 9,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,12</t>
+          <t>6,39; 12,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 13,5</t>
+          <t>4,87; 12,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,85</t>
+          <t>3,4; 7,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 13,17</t>
+          <t>7,0; 13,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,71</t>
+          <t>4,71; 9,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 8,67</t>
+          <t>5,02; 10,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,27</t>
+          <t>4,03; 7,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,38</t>
+          <t>6,08; 10,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,97</t>
+          <t>5,95; 9,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 9,53</t>
+          <t>5,47; 10,16</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 11,17</t>
+          <t>4,43; 10,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 17,64</t>
+          <t>7,68; 18,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,67</t>
+          <t>3,92; 10,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,59</t>
+          <t>4,24; 10,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 11,14</t>
+          <t>4,05; 11,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 14,77</t>
+          <t>6,33; 14,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,4</t>
+          <t>5,17; 12,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 15,3</t>
+          <t>8,42; 15,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,03</t>
+          <t>4,99; 10,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,18; 14,5</t>
+          <t>7,97; 14,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,05</t>
+          <t>5,12; 10,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,87</t>
+          <t>7,29; 11,44</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,53</t>
+          <t>3,62; 9,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,19; 20,04</t>
+          <t>11,19; 20,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,09; 10,62</t>
+          <t>4,3; 10,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,85</t>
+          <t>5,42; 11,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,99</t>
+          <t>3,26; 9,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 14,81</t>
+          <t>7,09; 14,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,42; 13,16</t>
+          <t>6,32; 13,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,52</t>
+          <t>5,27; 10,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,91</t>
+          <t>4,05; 8,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9,92; 15,72</t>
+          <t>9,96; 15,63</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 10,63</t>
+          <t>6,05; 11,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,01</t>
+          <t>6,07; 10,02</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 10,29</t>
+          <t>5,9; 10,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 10,79</t>
+          <t>6,45; 10,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 10,62</t>
+          <t>6,25; 10,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,78; 14,03</t>
+          <t>7,9; 14,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,41</t>
+          <t>4,48; 8,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,14</t>
+          <t>4,45; 8,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,72</t>
+          <t>5,81; 9,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 10,37</t>
+          <t>7,85; 12,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,53</t>
+          <t>5,67; 8,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,98</t>
+          <t>5,84; 8,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,61</t>
+          <t>6,7; 10,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,91</t>
+          <t>8,63; 12,11</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,38</t>
+          <t>6,38; 10,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,09</t>
+          <t>3,58; 6,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,93</t>
+          <t>5,34; 8,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,87</t>
+          <t>3,99; 7,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,01</t>
+          <t>6,89; 11,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,97</t>
+          <t>4,74; 8,12</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,41</t>
+          <t>7,84; 12,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,5</t>
+          <t>4,54; 7,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 10,03</t>
+          <t>7,19; 10,21</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,08</t>
+          <t>4,63; 7,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,03; 9,95</t>
+          <t>7,19; 10,19</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,99</t>
+          <t>4,58; 6,76</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,07; 7,82</t>
+          <t>6,11; 7,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,47</t>
+          <t>8,38; 10,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,76; 8,68</t>
+          <t>6,81; 8,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,75</t>
+          <t>6,27; 8,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,6; 7,33</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,5</t>
+          <t>7,3; 9,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,32</t>
+          <t>7,4; 9,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,09</t>
+          <t>6,98; 8,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,33</t>
+          <t>6,1; 7,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 9,59</t>
+          <t>8,17; 9,64</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7,35; 8,73</t>
+          <t>7,4; 8,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,71</t>
+          <t>6,89; 8,12</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45711</t>
+          <t>44686</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12605; 29953</t>
+          <t>12112; 29544</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26048; 50252</t>
+          <t>26868; 50636</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22554; 44517</t>
+          <t>22547; 43573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16324; 38851</t>
+          <t>15549; 35433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11680; 29185</t>
+          <t>11240; 29904</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22638; 45339</t>
+          <t>22249; 43578</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17028; 35792</t>
+          <t>17858; 37301</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14024; 27650</t>
+          <t>14912; 30768</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28117; 52831</t>
+          <t>27339; 51542</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53758; 85206</t>
+          <t>54293; 84629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44264; 72842</t>
+          <t>45686; 73732</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32568; 62335</t>
+          <t>33709; 57204</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>18891</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>34835</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>53726</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21319; 44013</t>
+          <t>21407; 45762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50497; 83581</t>
+          <t>50975; 83776</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25714; 49316</t>
+          <t>25349; 49445</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10251; 31534</t>
+          <t>10551; 30504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21543; 43157</t>
+          <t>22083; 43651</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33027; 57816</t>
+          <t>32886; 58499</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28071; 54670</t>
+          <t>27803; 52807</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24550; 47838</t>
+          <t>25572; 49514</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47928; 78616</t>
+          <t>50115; 81346</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>90112; 132005</t>
+          <t>88770; 129764</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58888; 94486</t>
+          <t>60458; 94899</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39422; 71993</t>
+          <t>40675; 72310</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>24291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32404</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53898</t>
+          <t>58969</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8067; 22822</t>
+          <t>7733; 24054</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26162; 48445</t>
+          <t>25114; 48181</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11897; 28660</t>
+          <t>12451; 29376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14252; 30829</t>
+          <t>16174; 36245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2872; 13331</t>
+          <t>2812; 12522</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25027; 48137</t>
+          <t>26020; 50918</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16981; 38744</t>
+          <t>16012; 37675</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24006; 43063</t>
+          <t>26251; 44519</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13364; 30412</t>
+          <t>13177; 30885</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56343; 88125</t>
+          <t>56744; 89370</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33358; 60001</t>
+          <t>32124; 58911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42877; 67005</t>
+          <t>46833; 73035</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>27420</t>
+          <t>30184</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53535</t>
+          <t>60402</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13301; 30502</t>
+          <t>13114; 31013</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15693; 36469</t>
+          <t>15041; 36285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23765; 44837</t>
+          <t>23652; 46083</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16083; 42201</t>
+          <t>18178; 47557</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12441; 29161</t>
+          <t>12641; 29155</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26392; 51090</t>
+          <t>27177; 51502</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18175; 37597</t>
+          <t>18237; 38083</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16063; 41195</t>
+          <t>21186; 44402</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28352; 53085</t>
+          <t>29396; 53509</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48009; 79128</t>
+          <t>46294; 79926</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46371; 75519</t>
+          <t>45064; 74253</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35902; 75101</t>
+          <t>43446; 80716</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12660</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23686</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36346</t>
+          <t>39544</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8471; 22713</t>
+          <t>9001; 22101</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17335; 37500</t>
+          <t>16338; 38961</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7584; 22543</t>
+          <t>8290; 23217</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7879; 18933</t>
+          <t>8724; 21089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8133; 23144</t>
+          <t>8415; 23922</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13853; 32435</t>
+          <t>13891; 31619</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11017; 27094</t>
+          <t>11293; 26960</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17975; 31924</t>
+          <t>19125; 34505</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20776; 41211</t>
+          <t>20516; 41083</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35362; 62668</t>
+          <t>34445; 61260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21902; 43191</t>
+          <t>21989; 43170</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27755; 45979</t>
+          <t>31552; 49502</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>40787</t>
+          <t>41588</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10516; 25801</t>
+          <t>9793; 25654</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>30657; 54902</t>
+          <t>30670; 55182</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10765; 27931</t>
+          <t>11303; 28439</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15370; 31947</t>
+          <t>14681; 31274</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8859; 25009</t>
+          <t>9054; 25467</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19963; 41333</t>
+          <t>19781; 40170</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17523; 35955</t>
+          <t>17270; 36101</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13014; 27051</t>
+          <t>13887; 26848</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22478; 43435</t>
+          <t>22214; 43977</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54883; 86935</t>
+          <t>55096; 86439</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31978; 57012</t>
+          <t>32453; 60386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30982; 52728</t>
+          <t>32432; 53571</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>65695</t>
+          <t>76935</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>62465</t>
+          <t>74992</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>128160</t>
+          <t>151928</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>36289; 63302</t>
+          <t>36260; 63227</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40576; 71521</t>
+          <t>42780; 72507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40571; 69709</t>
+          <t>41063; 71569</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>48568; 87601</t>
+          <t>56888; 101193</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28727; 53645</t>
+          <t>28614; 53037</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29914; 56485</t>
+          <t>30903; 57842</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38667; 67225</t>
+          <t>40171; 68618</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>29641; 88088</t>
+          <t>60626; 92826</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>70098; 106909</t>
+          <t>71062; 108884</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>81580; 121843</t>
+          <t>79172; 118943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88073; 129469</t>
+          <t>90262; 135216</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>83573; 160782</t>
+          <t>128705; 180715</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>43283</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>42563</t>
+          <t>47867</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>78436</t>
+          <t>91149</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>46880; 77090</t>
+          <t>47379; 75977</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27275; 55090</t>
+          <t>27849; 54325</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41061; 69502</t>
+          <t>41557; 69553</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>14827; 54511</t>
+          <t>31865; 57992</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>53779; 86238</t>
+          <t>53945; 87709</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38186; 65410</t>
+          <t>38917; 66622</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>64725; 102535</t>
+          <t>64787; 103279</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>33462; 53636</t>
+          <t>37723; 60032</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>108137; 153106</t>
+          <t>109791; 155760</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>73650; 113171</t>
+          <t>73929; 112596</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>112746; 159678</t>
+          <t>115386; 163481</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>46765; 98407</t>
+          <t>74506; 110131</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>228631</t>
+          <t>253669</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>261492</t>
+          <t>288323</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>490123</t>
+          <t>541992</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>198803; 256265</t>
+          <t>200192; 258625</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>286616; 357926</t>
+          <t>286621; 359400</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>229355; 294465</t>
+          <t>231227; 294228</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>175822; 267910</t>
+          <t>221574; 293991</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>189238; 247559</t>
+          <t>190866; 247570</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>262955; 336776</t>
+          <t>258865; 330169</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>261307; 330404</t>
+          <t>262304; 330691</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>214202; 295894</t>
+          <t>260374; 318892</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>400407; 487562</t>
+          <t>405828; 486224</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>566712; 667732</t>
+          <t>569144; 671198</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>510177; 605538</t>
+          <t>513221; 608988</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>424323; 548369</t>
+          <t>500101; 589879</t>
         </is>
       </c>
     </row>
